--- a/results/Int All Data 0.2/Rando_6_permute.xlsx
+++ b/results/Int All Data 0.2/Rando_6_permute.xlsx
@@ -440,177 +440,177 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8773021663068562</v>
+        <v>0.8772091118886325</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8792631330802253</v>
+        <v>0.8791390605225936</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8792631330802253</v>
+        <v>0.8791390605225936</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8809610660314151</v>
+        <v>0.8746333655921983</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8807985309809176</v>
+        <v>0.8734304821459589</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8714502841261569</v>
+        <v>0.8759441921635773</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8761495322464576</v>
+        <v>0.8759441921635773</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8754106801657608</v>
+        <v>0.8773790912925878</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8776036626219013</v>
+        <v>0.8775608575895184</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8776849301471501</v>
+        <v>0.8774795900642696</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8746097918062483</v>
+        <v>0.8768027742623886</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8742965085982282</v>
+        <v>0.8768027742623886</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8733566589741681</v>
+        <v>0.8736699421821881</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8731748926772376</v>
+        <v>0.8745595424204075</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8738014590932777</v>
+        <v>0.8735694434105065</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.874064492915457</v>
+        <v>0.8700538474900121</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8763889922826869</v>
+        <v>0.8690134990942704</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8763889922826869</v>
+        <v>0.8690134990942704</v>
       </c>
     </row>
     <row r="20">
@@ -620,1127 +620,1127 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8767525248765478</v>
+        <v>0.8695085485992209</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8763077247574381</v>
+        <v>0.8704986476091219</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8752363582222884</v>
+        <v>0.8674781011935779</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.873043375766148</v>
+        <v>0.866476215290702</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8745787736668403</v>
+        <v>0.8649097992506017</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8725173081217896</v>
+        <v>0.8655363656666418</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8725173081217896</v>
+        <v>0.8648669942182188</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8740837241618898</v>
+        <v>0.8645847291496067</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8740837241618898</v>
+        <v>0.8640586615052482</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8743970073699099</v>
+        <v>0.8659073426139606</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8745092930345666</v>
+        <v>0.8655940594059406</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8667156753269312</v>
+        <v>0.8656443087917814</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8667156753269312</v>
+        <v>0.8677175612298071</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8671294573066329</v>
+        <v>0.8602918186555497</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8671294573066329</v>
+        <v>0.8602918186555497</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8638148589295019</v>
+        <v>0.8602918186555497</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8651995086726718</v>
+        <v>0.8619897516067396</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8531365542569294</v>
+        <v>0.8619897516067396</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8509435718007891</v>
+        <v>0.8557551055857465</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8462561105734634</v>
+        <v>0.8543202064567359</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8523592396833668</v>
+        <v>0.8527848085560435</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8504292910494057</v>
+        <v>0.8479850616640612</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8496209583364351</v>
+        <v>0.8479850616640612</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8517636914067346</v>
+        <v>0.8501277947343606</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8505105585746544</v>
+        <v>0.8499460284374302</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8505105585746544</v>
+        <v>0.8421182907764461</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.849996277823271</v>
+        <v>0.8473436065411053</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8517444601603017</v>
+        <v>0.8485967393731855</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8489751606739622</v>
+        <v>0.8568233703069555</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.84869289560535</v>
+        <v>0.8606832675748778</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8475712796843594</v>
+        <v>0.863572297079332</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.843761631802278</v>
+        <v>0.8616733665847788</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8440749150102981</v>
+        <v>0.8613600833767587</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8443881982183181</v>
+        <v>0.864280131020621</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8450147646343582</v>
+        <v>0.8665233628626021</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8447014814263382</v>
+        <v>0.8657150301496315</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.845096032159607</v>
+        <v>0.862249683614978</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8799827539144892</v>
+        <v>0.8593178490781409</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8780217871411202</v>
+        <v>0.8608147844859675</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8774957194967618</v>
+        <v>0.8597936673366585</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.876424352961612</v>
+        <v>0.8597936673366585</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8783040522097323</v>
+        <v>0.8585405345045782</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8770627062706271</v>
+        <v>0.8698882106255739</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8706965433385444</v>
+        <v>0.8721816918533959</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8787916573612249</v>
+        <v>0.8669873942281446</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8787916573612249</v>
+        <v>0.8664923447231941</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8775385245291447</v>
+        <v>0.8619364004069581</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8811161567284549</v>
+        <v>0.8738796248045857</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8819480632273754</v>
+        <v>0.8738796248045857</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8812712474254945</v>
+        <v>0.8465886250279163</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8812712474254945</v>
+        <v>0.8465886250279163</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8761464304325169</v>
+        <v>0.8419203950470235</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8825938608898484</v>
+        <v>0.8409805454229633</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8921046427951066</v>
+        <v>0.8424464626913819</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8922051415667882</v>
+        <v>0.8442759125536614</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8842105263157896</v>
+        <v>0.8458423285937616</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8954000099258046</v>
+        <v>0.8424464626913819</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8930755105585746</v>
+        <v>0.8477530459812899</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.884059778158267</v>
+        <v>0.84869289560535</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8845238095238095</v>
+        <v>0.8493697114072309</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8845238095238095</v>
+        <v>0.8495514777041614</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8799560783145983</v>
+        <v>0.8539374426164421</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8793295118985582</v>
+        <v>0.8586056725973349</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.880764411027569</v>
+        <v>0.8579791061812948</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.8841795081763816</v>
+        <v>0.8573835579046627</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8826633415221221</v>
+        <v>0.8508046105362416</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.8831583910270726</v>
+        <v>0.8370468249832501</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.8789039430258816</v>
+        <v>0.8370468249832501</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.8785906598178614</v>
+        <v>0.8462635549269213</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.8737096454006303</v>
+        <v>0.8379246383284945</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.8757208615598402</v>
+        <v>0.8398545869624556</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.8737909129258791</v>
+        <v>0.8382379215365146</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.8749125288468697</v>
+        <v>0.8425736370629544</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.8720619618352813</v>
+        <v>0.8480812178962257</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.8663415965656716</v>
+        <v>0.8400673713987941</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.868534579021812</v>
+        <v>0.8258381101268022</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.8815609568475644</v>
+        <v>0.8175612298071913</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.8815609568475644</v>
+        <v>0.8211891113923422</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.8801260577185539</v>
+        <v>0.7478188044368347</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.8754770589840939</v>
+        <v>0.7553376014293158</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.8796310082136034</v>
+        <v>0.7599363507779349</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.8873625896424229</v>
+        <v>0.7692033301074468</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.8932454899625302</v>
+        <v>0.7616845331149656</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.8906889749125289</v>
+        <v>0.5659830268741159</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.8863147968932232</v>
+        <v>0.5741283902826373</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.8769442169780888</v>
+        <v>0.5586149780391573</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.8605188714360158</v>
+        <v>0.5586149780391573</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.8566087247822527</v>
+        <v>0.5514094642546962</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.865357080820864</v>
+        <v>0.5585647286533164</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.8641734286210576</v>
+        <v>0.5601311446934167</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.8649817613340282</v>
+        <v>0.5614655450507456</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.864749745651257</v>
+        <v>0.5578879128514355</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.8327948584332118</v>
+        <v>0.5417789523313233</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.8275620983150946</v>
+        <v>0.5261147919303208</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.8097552048437926</v>
+        <v>0.5169985607583315</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.8132013201320132</v>
+        <v>0.5109649122807017</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.8111398545869625</v>
+        <v>0.5119047619047619</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.7668720067495471</v>
+        <v>0.5097117794486216</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.7668720067495471</v>
+        <v>0.5043859649122807</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.7670035236606367</v>
+        <v>0.5034461152882206</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.7666784535596416</v>
+        <v>0.5056390977443609</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.762335293679744</v>
+        <v>0.5056390977443609</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.7466016526464676</v>
+        <v>0.5056390977443609</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.7466016526464676</v>
+        <v>0.5056390977443609</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.7363253430606218</v>
+        <v>0.5068922305764411</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.7050665028908907</v>
+        <v>0.5034461152882206</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.7256842601553388</v>
+        <v>0.5034461152882206</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.7225514280751384</v>
+        <v>0.5012531328320802</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.696599171195315</v>
+        <v>0.5012531328320802</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.7056415791955135</v>
+        <v>0.5012531328320802</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.7641535770118365</v>
+        <v>0.5009398496240601</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.7716649296508598</v>
+        <v>0.5006265664160401</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.7716649296508598</v>
+        <v>0.5009398496240601</v>
       </c>
     </row>
     <row r="133">
@@ -1750,237 +1750,237 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.7545925457207374</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.7576751284150971</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.7086906622993127</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.6827750068239906</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.6911598302687412</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.6993126380307204</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.6986860716146803</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.6418149333730365</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.6430680662051167</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.6188211866299412</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5631982183180724</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5090721854140301</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5252407007618055</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5374084964887467</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5382980967269659</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5390828556539864</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5256042333556664</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5249274175537855</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5242195836124965</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5203950470234993</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5194551973994392</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5049560783145984</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5048245614035087</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5057867440879427</v>
+        <v>0.5007580833271297</v>
       </c>
     </row>
   </sheetData>
